--- a/docs/informe/Project Charter.xlsx
+++ b/docs/informe/Project Charter.xlsx
@@ -100,7 +100,7 @@
     <t>Modalidad de entrega</t>
   </si>
   <si>
-    <t>Recojo presencial. No se operará delivery propio; una integración con empresas externas queda como evaluación futura.</t>
+    <t>Recojo presencial. No se operará delivery propio; la integración con empresas externas de delivery es una función futura prevista para el avance final.</t>
   </si>
   <si>
     <t>Servicios no incluidos</t>
